--- a/ebegu-server/src/main/resources/reporting/Ferienbetreuung.xlsx
+++ b/ebegu-server/src/main/resources/reporting/Ferienbetreuung.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\enja\IdeaProjects\ebegu\ebegu-server\src\main\resources\reporting\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/frederic.nell/IdeaProjects/kibon-app/ebegu-server/src/main/resources/reporting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21176E94-1585-4B14-BE1C-4DCBDC5C0C3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFFA49E3-BE2D-5B4A-A43B-D9B3297F4CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="19980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="188">
   <si>
     <t>Ferienbetreuungen</t>
   </si>
@@ -592,6 +592,12 @@
   </si>
   <si>
     <t>{eigenleistungenGemeinde}</t>
+  </si>
+  <si>
+    <t>0_eingereicht_am</t>
+  </si>
+  <si>
+    <t>{firstEinreicheDatum}</t>
   </si>
 </sst>
 </file>
@@ -722,7 +728,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -738,9 +744,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -778,7 +784,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -884,7 +890,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1026,7 +1032,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1034,99 +1040,99 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CK8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:CL8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.5546875" style="7" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="35.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="32.44140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="34.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="33.33203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="32" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="31.33203125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="32.6640625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="16.5546875" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="7" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="16.5546875" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="13" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="12" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="16.5546875" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="69" max="72" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="18" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="23.88671875" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="21.44140625" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="79" max="79" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="81" max="84" width="21.5546875" customWidth="1"/>
-    <col min="85" max="85" width="16.5546875" bestFit="1" customWidth="1"/>
-    <col min="86" max="86" width="20.88671875" bestFit="1" customWidth="1"/>
-    <col min="87" max="87" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="88" max="88" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="19.5" style="7" customWidth="1"/>
+    <col min="7" max="7" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="32.5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="34.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="33.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="32" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="31.33203125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="7" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="13" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="12" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="70" max="73" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="18" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="82" max="85" width="21.5" customWidth="1"/>
+    <col min="86" max="86" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="87" max="87" width="20.83203125" bestFit="1" customWidth="1"/>
+    <col min="88" max="88" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="89" max="89" width="13.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:89" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:90" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:89" ht="21" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:90" ht="21" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:89" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:90" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
@@ -1134,14 +1140,13 @@
         <v>170</v>
       </c>
     </row>
-    <row r="4" spans="1:89" ht="21" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:90" ht="21" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
     </row>
-    <row r="6" spans="1:89" x14ac:dyDescent="0.3">
-      <c r="F6" s="10" t="s">
+    <row r="6" spans="1:90" x14ac:dyDescent="0.2">
+      <c r="G6" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="G6" s="11"/>
       <c r="H6" s="11"/>
       <c r="I6" s="11"/>
       <c r="J6" s="11"/>
@@ -1161,11 +1166,11 @@
       <c r="X6" s="11"/>
       <c r="Y6" s="11"/>
       <c r="Z6" s="11"/>
-      <c r="AA6" s="12"/>
-      <c r="AB6" s="10" t="s">
+      <c r="AA6" s="11"/>
+      <c r="AB6" s="12"/>
+      <c r="AC6" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="AC6" s="11"/>
       <c r="AD6" s="11"/>
       <c r="AE6" s="11"/>
       <c r="AF6" s="11"/>
@@ -1198,11 +1203,11 @@
       <c r="BG6" s="11"/>
       <c r="BH6" s="11"/>
       <c r="BI6" s="11"/>
-      <c r="BJ6" s="12"/>
-      <c r="BK6" s="10" t="s">
+      <c r="BJ6" s="11"/>
+      <c r="BK6" s="12"/>
+      <c r="BL6" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="BL6" s="11"/>
       <c r="BM6" s="11"/>
       <c r="BN6" s="11"/>
       <c r="BO6" s="11"/>
@@ -1210,30 +1215,31 @@
       <c r="BQ6" s="11"/>
       <c r="BR6" s="11"/>
       <c r="BS6" s="11"/>
-      <c r="BT6" s="12"/>
-      <c r="BU6" s="10" t="s">
+      <c r="BT6" s="11"/>
+      <c r="BU6" s="12"/>
+      <c r="BV6" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="BV6" s="11"/>
       <c r="BW6" s="11"/>
       <c r="BX6" s="11"/>
       <c r="BY6" s="11"/>
       <c r="BZ6" s="11"/>
       <c r="CA6" s="11"/>
       <c r="CB6" s="11"/>
-      <c r="CC6" s="10" t="s">
+      <c r="CC6" s="11"/>
+      <c r="CD6" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="CD6" s="11"/>
       <c r="CE6" s="11"/>
-      <c r="CF6" s="12"/>
-      <c r="CG6" s="10" t="s">
+      <c r="CF6" s="11"/>
+      <c r="CG6" s="12"/>
+      <c r="CH6" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="CH6" s="11"/>
-      <c r="CI6" s="12"/>
+      <c r="CI6" s="11"/>
+      <c r="CJ6" s="12"/>
     </row>
-    <row r="7" spans="1:89" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:90" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
@@ -1249,257 +1255,260 @@
       <c r="E7" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="I7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="J7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="K7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="L7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="M7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="N7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="O7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="O7" s="2" t="s">
+      <c r="P7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="P7" s="2" t="s">
+      <c r="Q7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="Q7" s="2" t="s">
+      <c r="R7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="R7" s="2" t="s">
+      <c r="S7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="S7" s="2" t="s">
+      <c r="T7" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="T7" s="2" t="s">
+      <c r="U7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="U7" s="2" t="s">
+      <c r="V7" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="V7" s="2" t="s">
+      <c r="W7" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="W7" s="2" t="s">
+      <c r="X7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="X7" s="2" t="s">
+      <c r="Y7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="Y7" s="2" t="s">
+      <c r="Z7" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="Z7" s="2" t="s">
+      <c r="AA7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AA7" s="2" t="s">
+      <c r="AB7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AB7" s="2" t="s">
+      <c r="AC7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AC7" s="2" t="s">
+      <c r="AD7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="AD7" s="2" t="s">
+      <c r="AE7" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="AE7" s="2" t="s">
+      <c r="AF7" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AF7" s="2" t="s">
+      <c r="AG7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AG7" s="2" t="s">
+      <c r="AH7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AH7" s="2" t="s">
+      <c r="AI7" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AI7" s="2" t="s">
+      <c r="AJ7" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="AJ7" s="2" t="s">
+      <c r="AK7" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AK7" s="2" t="s">
+      <c r="AL7" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AL7" s="2" t="s">
+      <c r="AM7" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AM7" s="2" t="s">
+      <c r="AN7" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AN7" s="2" t="s">
+      <c r="AO7" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="AO7" s="2" t="s">
+      <c r="AP7" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AP7" s="2" t="s">
+      <c r="AQ7" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AQ7" s="2" t="s">
+      <c r="AR7" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="AR7" s="2" t="s">
+      <c r="AS7" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="AS7" s="2" t="s">
+      <c r="AT7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="AT7" s="2" t="s">
+      <c r="AU7" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AU7" s="2" t="s">
+      <c r="AV7" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="AV7" s="2" t="s">
+      <c r="AW7" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="AW7" s="2" t="s">
+      <c r="AX7" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="AX7" s="2" t="s">
+      <c r="AY7" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="AY7" s="2" t="s">
+      <c r="AZ7" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="AZ7" s="2" t="s">
+      <c r="BA7" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="BA7" s="2" t="s">
+      <c r="BB7" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="BB7" s="2" t="s">
+      <c r="BC7" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="BC7" s="2" t="s">
+      <c r="BD7" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="BD7" s="2" t="s">
+      <c r="BE7" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="BE7" s="2" t="s">
+      <c r="BF7" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="BF7" s="2" t="s">
+      <c r="BG7" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="BG7" s="2" t="s">
+      <c r="BH7" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="BH7" s="2" t="s">
+      <c r="BI7" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="BI7" s="2" t="s">
+      <c r="BJ7" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="BJ7" s="2" t="s">
+      <c r="BK7" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="BK7" s="2" t="s">
+      <c r="BL7" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="BL7" s="2" t="s">
+      <c r="BM7" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="BM7" s="2" t="s">
+      <c r="BN7" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="BN7" s="2" t="s">
+      <c r="BO7" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="BO7" s="2" t="s">
+      <c r="BP7" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="BP7" s="2" t="s">
+      <c r="BQ7" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="BQ7" s="2" t="s">
+      <c r="BR7" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="BR7" s="2" t="s">
+      <c r="BS7" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="BS7" s="2" t="s">
+      <c r="BT7" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="BT7" s="2" t="s">
+      <c r="BU7" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="BU7" s="2" t="s">
+      <c r="BV7" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="BV7" s="2" t="s">
+      <c r="BW7" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="BW7" s="2" t="s">
+      <c r="BX7" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="BX7" s="2" t="s">
+      <c r="BY7" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="BY7" s="2" t="s">
+      <c r="BZ7" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="BZ7" s="2" t="s">
+      <c r="CA7" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="CA7" s="2" t="s">
+      <c r="CB7" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="CB7" s="2" t="s">
+      <c r="CC7" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="CC7" s="2" t="s">
+      <c r="CD7" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="CD7" s="2" t="s">
+      <c r="CE7" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="CE7" s="2" t="s">
+      <c r="CF7" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="CF7" s="2" t="s">
+      <c r="CG7" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="CG7" s="2" t="s">
+      <c r="CH7" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="CH7" s="2" t="s">
+      <c r="CI7" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="CI7" s="2" t="s">
+      <c r="CJ7" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="CJ7" s="2" t="s">
+      <c r="CK7" s="2" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="8" spans="1:89" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:90" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>89</v>
       </c>
@@ -1515,267 +1524,270 @@
       <c r="E8" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="I8" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="K8" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="L8" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="L8" s="3" t="s">
+      <c r="M8" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="M8" s="3" t="s">
+      <c r="N8" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="N8" s="3" t="s">
+      <c r="O8" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="O8" s="3" t="s">
+      <c r="P8" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="P8" s="3" t="s">
+      <c r="Q8" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="Q8" s="3" t="s">
+      <c r="R8" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="R8" s="3" t="s">
+      <c r="S8" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="S8" s="3" t="s">
+      <c r="T8" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="T8" s="3" t="s">
+      <c r="U8" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="U8" s="3" t="s">
+      <c r="V8" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="V8" s="3" t="s">
+      <c r="W8" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="W8" s="3" t="s">
+      <c r="X8" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="X8" s="3" t="s">
+      <c r="Y8" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="Y8" s="3" t="s">
+      <c r="Z8" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="Z8" s="3" t="s">
+      <c r="AA8" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="AA8" s="3" t="s">
+      <c r="AB8" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="AB8" s="3" t="s">
+      <c r="AC8" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="AC8" s="3" t="s">
+      <c r="AD8" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="AD8" s="3" t="s">
+      <c r="AE8" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="AE8" s="3" t="s">
+      <c r="AF8" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="AF8" s="3" t="s">
+      <c r="AG8" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="AG8" s="3" t="s">
+      <c r="AH8" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="AH8" s="3" t="s">
+      <c r="AI8" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="AI8" s="3" t="s">
+      <c r="AJ8" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="AJ8" s="6" t="s">
+      <c r="AK8" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="AK8" s="6" t="s">
+      <c r="AL8" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="AL8" s="6" t="s">
+      <c r="AM8" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="AM8" s="6" t="s">
+      <c r="AN8" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="AN8" s="6" t="s">
+      <c r="AO8" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="AO8" s="6" t="s">
+      <c r="AP8" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="AP8" s="3" t="s">
+      <c r="AQ8" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="AQ8" s="6" t="s">
+      <c r="AR8" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="AR8" s="3" t="s">
+      <c r="AS8" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="AS8" s="3" t="s">
+      <c r="AT8" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="AT8" s="3" t="s">
+      <c r="AU8" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="AU8" s="3" t="s">
+      <c r="AV8" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="AV8" s="3" t="s">
+      <c r="AW8" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="AW8" s="3" t="s">
+      <c r="AX8" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="AX8" s="3" t="s">
+      <c r="AY8" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="AY8" s="3" t="s">
+      <c r="AZ8" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="AZ8" s="3" t="s">
+      <c r="BA8" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="BA8" s="3" t="s">
+      <c r="BB8" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="BB8" s="3" t="s">
+      <c r="BC8" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="BC8" s="3" t="s">
+      <c r="BD8" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="BD8" s="3" t="s">
+      <c r="BE8" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="BE8" s="3" t="s">
+      <c r="BF8" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="BF8" s="3" t="s">
+      <c r="BG8" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="BG8" s="3" t="s">
+      <c r="BH8" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="BH8" s="3" t="s">
+      <c r="BI8" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="BI8" s="3" t="s">
+      <c r="BJ8" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="BJ8" s="3" t="s">
+      <c r="BK8" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="BK8" s="6" t="s">
+      <c r="BL8" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="BL8" s="6" t="s">
+      <c r="BM8" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="BM8" s="6" t="s">
+      <c r="BN8" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="BN8" s="6" t="s">
+      <c r="BO8" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="BO8" s="6" t="s">
+      <c r="BP8" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="BP8" s="6" t="s">
+      <c r="BQ8" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="BQ8" s="6" t="s">
+      <c r="BR8" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="BR8" s="6" t="s">
+      <c r="BS8" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="BS8" s="6" t="s">
+      <c r="BT8" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="BT8" s="6" t="s">
+      <c r="BU8" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="BU8" s="6" t="s">
+      <c r="BV8" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="BV8" s="6" t="s">
+      <c r="BW8" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="BW8" s="6" t="s">
+      <c r="BX8" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="BX8" s="6" t="s">
+      <c r="BY8" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="BY8" s="6" t="s">
+      <c r="BZ8" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="BZ8" s="6" t="s">
+      <c r="CA8" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="CA8" s="6" t="s">
+      <c r="CB8" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="CB8" s="6" t="s">
+      <c r="CC8" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="CC8" s="6" t="s">
+      <c r="CD8" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="CD8" s="6" t="s">
+      <c r="CE8" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="CE8" s="6" t="s">
+      <c r="CF8" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="CF8" s="6" t="s">
+      <c r="CG8" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="CG8" s="6" t="s">
+      <c r="CH8" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="CH8" s="6" t="s">
+      <c r="CI8" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="CI8" s="6" t="s">
+      <c r="CJ8" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="CJ8" s="3" t="s">
+      <c r="CK8" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="CK8" t="s">
+      <c r="CL8" t="s">
         <v>169</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="CG6:CI6"/>
-    <mergeCell ref="AB6:BJ6"/>
-    <mergeCell ref="BK6:BT6"/>
-    <mergeCell ref="F6:AA6"/>
-    <mergeCell ref="BU6:CB6"/>
-    <mergeCell ref="CC6:CF6"/>
+    <mergeCell ref="CH6:CJ6"/>
+    <mergeCell ref="AC6:BK6"/>
+    <mergeCell ref="BL6:BU6"/>
+    <mergeCell ref="G6:AB6"/>
+    <mergeCell ref="BV6:CC6"/>
+    <mergeCell ref="CD6:CG6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
